--- a/teacher_forms/007_remote_learning_survey_for_kindergarten_kids--teacher_forms.xlsx
+++ b/teacher_forms/007_remote_learning_survey_for_kindergarten_kids--teacher_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -619,8 +619,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -648,12 +648,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'very_effective',_'label':_'very_effective'}</t>
+          <t>very_effective</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'very effective', 'label': 'Very Effective'}</t>
+          <t>Very Effective</t>
         </is>
       </c>
     </row>
@@ -665,12 +665,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'not_effective',_'label':_'not_effective'}</t>
+          <t>not_effective</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'not effective', 'label': 'Not Effective'}</t>
+          <t>Not Effective</t>
         </is>
       </c>
     </row>
@@ -682,12 +682,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'neutral',_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'neutral', 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'communication',_'label':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'communication', 'label': 'Communication'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'engagement',_'label':_'engagement'}</t>
+          <t>engagement</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'engagement', 'label': 'Engagement'}</t>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
@@ -733,12 +733,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'organization',_'label':_'organization'}</t>
+          <t>organization</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'organization', 'label': 'Organization'}</t>
+          <t>Organization</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'resources',_'label':_'resources'}</t>
+          <t>resources</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'resources', 'label': 'Resources'}</t>
+          <t>Resources</t>
         </is>
       </c>
     </row>
